--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA20ADFC-CD05-47A4-9DE8-0ADA7E302237}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839DDFEF-FE8E-4D7E-B7EA-72F916047331}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,16 +178,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -545,26 +545,26 @@
       <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="I3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
@@ -605,10 +605,10 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>46235</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1">
@@ -646,10 +646,10 @@
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>46236</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1">
@@ -687,10 +687,10 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>46237</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="1">
@@ -728,41 +728,52 @@
       <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>46238</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1">
         <v>45</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1">
+        <f>73.4+17.5</f>
+        <v>90.9</v>
+      </c>
       <c r="F8" s="1">
         <v>35.1</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>23.5</v>
+      </c>
       <c r="H8" s="1">
         <v>30</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>56.2</v>
+      </c>
       <c r="J8" s="1">
         <v>12</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <v>27.8</v>
+      </c>
       <c r="L8" s="1">
         <v>13.5</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1">
+        <v>32.799999999999997</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="3">
         <v>46239</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1">
@@ -790,10 +801,10 @@
       <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>46240</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="1">
@@ -821,10 +832,10 @@
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>46241</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="1">
@@ -852,10 +863,10 @@
       <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>46242</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="1">
@@ -883,10 +894,10 @@
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>46243</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1">
@@ -914,10 +925,10 @@
       <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="3">
         <v>46244</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="1">
@@ -945,10 +956,10 @@
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="3">
         <v>46245</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="1">
@@ -976,10 +987,10 @@
       <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="3">
         <v>46246</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="1">
@@ -1007,10 +1018,10 @@
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="3">
         <v>46247</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="1">
@@ -1038,10 +1049,10 @@
       <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="3">
         <v>46248</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="1">
@@ -1069,10 +1080,10 @@
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="3">
         <v>46249</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="1">
@@ -1100,10 +1111,10 @@
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="3">
         <v>46250</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="1">
@@ -1131,10 +1142,10 @@
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="3">
         <v>46251</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="1">
@@ -1162,10 +1173,10 @@
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="3">
         <v>46252</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="1">
@@ -1193,10 +1204,10 @@
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="3">
         <v>46253</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="1">
@@ -1224,10 +1235,10 @@
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="3">
         <v>46254</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="1">
@@ -1255,10 +1266,10 @@
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="3">
         <v>46255</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="1">
@@ -1286,10 +1297,10 @@
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="3">
         <v>46256</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="1">
@@ -1317,10 +1328,10 @@
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="3">
         <v>46257</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="1">
@@ -1348,10 +1359,10 @@
       <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="3">
         <v>46258</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="1">
@@ -1379,10 +1390,10 @@
       <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="3">
         <v>46259</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="1">
@@ -1410,10 +1421,10 @@
       <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="3">
         <v>46260</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="1">
@@ -1441,10 +1452,10 @@
       <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="3">
         <v>46261</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D31" s="1">
@@ -1472,10 +1483,10 @@
       <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="3">
         <v>46262</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="1">
@@ -1503,10 +1514,10 @@
       <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="3">
         <v>46263</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="1">
@@ -1534,10 +1545,10 @@
       <c r="A34" s="1">
         <v>30</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="3">
         <v>46264</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="1">
@@ -1565,10 +1576,10 @@
       <c r="A35" s="1">
         <v>30</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="3">
         <v>46265</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="1">
@@ -1593,21 +1604,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1660,26 +1671,26 @@
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5" t="s">
+      <c r="E40" s="6"/>
+      <c r="F40" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5" t="s">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5" t="s">
+      <c r="I40" s="6"/>
+      <c r="J40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M40" s="5"/>
+      <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
@@ -1720,10 +1731,10 @@
       <c r="A42" s="1">
         <v>1</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="3">
         <v>46235</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="1">
@@ -1761,10 +1772,10 @@
       <c r="A43" s="2">
         <v>2</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="3">
         <v>46236</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="1">
@@ -1802,10 +1813,10 @@
       <c r="A44" s="1">
         <v>3</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="3">
         <v>46237</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="1">
@@ -1843,41 +1854,52 @@
       <c r="A45" s="2">
         <v>4</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="3">
         <v>46238</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="1">
         <v>15</v>
       </c>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1">
+        <f>14.1+15.6</f>
+        <v>29.7</v>
+      </c>
       <c r="F45" s="1">
         <v>15</v>
       </c>
-      <c r="G45" s="1"/>
+      <c r="G45" s="1">
+        <v>10.9</v>
+      </c>
       <c r="H45" s="1">
         <v>7.4</v>
       </c>
-      <c r="I45" s="1"/>
+      <c r="I45" s="1">
+        <v>11</v>
+      </c>
       <c r="J45" s="1">
         <v>8</v>
       </c>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1">
+        <v>11.8</v>
+      </c>
       <c r="L45" s="1">
         <v>2.8</v>
       </c>
-      <c r="M45" s="1"/>
+      <c r="M45" s="1">
+        <v>9.8000000000000007</v>
+      </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="3">
         <v>46239</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="1">
@@ -1905,10 +1927,10 @@
       <c r="A47" s="2">
         <v>6</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="3">
         <v>46240</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D47" s="1">
@@ -1936,10 +1958,10 @@
       <c r="A48" s="1">
         <v>7</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="3">
         <v>46241</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="1">
@@ -1967,10 +1989,10 @@
       <c r="A49" s="2">
         <v>8</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="3">
         <v>46242</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="1">
@@ -1998,10 +2020,10 @@
       <c r="A50" s="1">
         <v>9</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="3">
         <v>46243</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D50" s="1">
@@ -2029,10 +2051,10 @@
       <c r="A51" s="2">
         <v>10</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="3">
         <v>46244</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="1">
@@ -2060,10 +2082,10 @@
       <c r="A52" s="1">
         <v>11</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="3">
         <v>46245</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="1">
@@ -2091,10 +2113,10 @@
       <c r="A53" s="2">
         <v>12</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="3">
         <v>46246</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="1">
@@ -2122,10 +2144,10 @@
       <c r="A54" s="1">
         <v>13</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="3">
         <v>46247</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D54" s="1">
@@ -2153,10 +2175,10 @@
       <c r="A55" s="2">
         <v>14</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="3">
         <v>46248</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="1">
@@ -2184,10 +2206,10 @@
       <c r="A56" s="1">
         <v>15</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="3">
         <v>46249</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="1">
@@ -2215,10 +2237,10 @@
       <c r="A57" s="1">
         <v>16</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="3">
         <v>46250</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D57" s="1">
@@ -2246,10 +2268,10 @@
       <c r="A58" s="1">
         <v>17</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="3">
         <v>46251</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="1">
@@ -2277,10 +2299,10 @@
       <c r="A59" s="1">
         <v>18</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="3">
         <v>46252</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D59" s="1">
@@ -2308,10 +2330,10 @@
       <c r="A60" s="1">
         <v>19</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="3">
         <v>46253</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="1">
@@ -2339,10 +2361,10 @@
       <c r="A61" s="1">
         <v>20</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="3">
         <v>46254</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D61" s="1">
@@ -2370,10 +2392,10 @@
       <c r="A62" s="1">
         <v>21</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="3">
         <v>46255</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="1">
@@ -2401,10 +2423,10 @@
       <c r="A63" s="1">
         <v>22</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="3">
         <v>46256</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="1">
@@ -2432,10 +2454,10 @@
       <c r="A64" s="1">
         <v>23</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="3">
         <v>46257</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="1">
@@ -2463,10 +2485,10 @@
       <c r="A65" s="1">
         <v>24</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="3">
         <v>46258</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="1">
@@ -2494,10 +2516,10 @@
       <c r="A66" s="1">
         <v>25</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="3">
         <v>46259</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="1">
@@ -2525,10 +2547,10 @@
       <c r="A67" s="1">
         <v>26</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="3">
         <v>46260</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="1">
@@ -2556,10 +2578,10 @@
       <c r="A68" s="1">
         <v>27</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B68" s="3">
         <v>46261</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="1">
@@ -2587,10 +2609,10 @@
       <c r="A69" s="1">
         <v>28</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69" s="3">
         <v>46262</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D69" s="1">
@@ -2618,10 +2640,10 @@
       <c r="A70" s="1">
         <v>29</v>
       </c>
-      <c r="B70" s="6">
+      <c r="B70" s="3">
         <v>46263</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="1">
@@ -2649,10 +2671,10 @@
       <c r="A71" s="1">
         <v>30</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="3">
         <v>46264</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D71" s="1">
@@ -2680,10 +2702,10 @@
       <c r="A72" s="1">
         <v>30</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B72" s="3">
         <v>46265</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D72" s="1">
@@ -2708,21 +2730,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2775,26 +2797,26 @@
       <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5" t="s">
+      <c r="E76" s="6"/>
+      <c r="F76" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5" t="s">
+      <c r="G76" s="6"/>
+      <c r="H76" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5" t="s">
+      <c r="I76" s="6"/>
+      <c r="J76" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M76" s="5"/>
+      <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
@@ -2835,10 +2857,10 @@
       <c r="A78" s="1">
         <v>1</v>
       </c>
-      <c r="B78" s="6">
+      <c r="B78" s="3">
         <v>46235</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="1">
@@ -2876,10 +2898,10 @@
       <c r="A79" s="2">
         <v>2</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="3">
         <v>46236</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="1">
@@ -2917,10 +2939,10 @@
       <c r="A80" s="1">
         <v>3</v>
       </c>
-      <c r="B80" s="6">
+      <c r="B80" s="3">
         <v>46237</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="1">
@@ -2958,41 +2980,52 @@
       <c r="A81" s="2">
         <v>4</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="3">
         <v>46238</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D81" s="1">
         <v>22</v>
       </c>
-      <c r="E81" s="1"/>
+      <c r="E81" s="1">
+        <f>35.6+5.9</f>
+        <v>41.5</v>
+      </c>
       <c r="F81" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G81" s="1"/>
+      <c r="G81" s="1">
+        <v>5.9</v>
+      </c>
       <c r="H81" s="1">
         <v>3.7</v>
       </c>
-      <c r="I81" s="1"/>
+      <c r="I81" s="1">
+        <v>13.4</v>
+      </c>
       <c r="J81" s="1">
         <v>5</v>
       </c>
-      <c r="K81" s="1"/>
+      <c r="K81" s="1">
+        <v>12.5</v>
+      </c>
       <c r="L81" s="1">
         <v>2.7</v>
       </c>
-      <c r="M81" s="1"/>
+      <c r="M81" s="1">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>5</v>
       </c>
-      <c r="B82" s="6">
+      <c r="B82" s="3">
         <v>46239</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="1">
@@ -3020,10 +3053,10 @@
       <c r="A83" s="2">
         <v>6</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="3">
         <v>46240</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D83" s="1">
@@ -3051,10 +3084,10 @@
       <c r="A84" s="1">
         <v>7</v>
       </c>
-      <c r="B84" s="6">
+      <c r="B84" s="3">
         <v>46241</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D84" s="1">
@@ -3082,10 +3115,10 @@
       <c r="A85" s="2">
         <v>8</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="3">
         <v>46242</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="1">
@@ -3113,10 +3146,10 @@
       <c r="A86" s="1">
         <v>9</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B86" s="3">
         <v>46243</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="1">
@@ -3144,10 +3177,10 @@
       <c r="A87" s="2">
         <v>10</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="3">
         <v>46244</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="1">
@@ -3175,10 +3208,10 @@
       <c r="A88" s="1">
         <v>11</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B88" s="3">
         <v>46245</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D88" s="1">
@@ -3206,10 +3239,10 @@
       <c r="A89" s="2">
         <v>12</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="3">
         <v>46246</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D89" s="1">
@@ -3237,10 +3270,10 @@
       <c r="A90" s="1">
         <v>13</v>
       </c>
-      <c r="B90" s="6">
+      <c r="B90" s="3">
         <v>46247</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D90" s="1">
@@ -3268,10 +3301,10 @@
       <c r="A91" s="2">
         <v>14</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="3">
         <v>46248</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D91" s="1">
@@ -3299,10 +3332,10 @@
       <c r="A92" s="1">
         <v>15</v>
       </c>
-      <c r="B92" s="6">
+      <c r="B92" s="3">
         <v>46249</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="1">
@@ -3330,10 +3363,10 @@
       <c r="A93" s="1">
         <v>16</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="3">
         <v>46250</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="1">
@@ -3361,10 +3394,10 @@
       <c r="A94" s="1">
         <v>17</v>
       </c>
-      <c r="B94" s="6">
+      <c r="B94" s="3">
         <v>46251</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D94" s="1">
@@ -3392,10 +3425,10 @@
       <c r="A95" s="1">
         <v>18</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="3">
         <v>46252</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D95" s="1">
@@ -3423,10 +3456,10 @@
       <c r="A96" s="1">
         <v>19</v>
       </c>
-      <c r="B96" s="6">
+      <c r="B96" s="3">
         <v>46253</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D96" s="1">
@@ -3454,10 +3487,10 @@
       <c r="A97" s="1">
         <v>20</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="3">
         <v>46254</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D97" s="1">
@@ -3485,10 +3518,10 @@
       <c r="A98" s="1">
         <v>21</v>
       </c>
-      <c r="B98" s="6">
+      <c r="B98" s="3">
         <v>46255</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D98" s="1">
@@ -3516,10 +3549,10 @@
       <c r="A99" s="1">
         <v>22</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="3">
         <v>46256</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D99" s="1">
@@ -3547,10 +3580,10 @@
       <c r="A100" s="1">
         <v>23</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B100" s="3">
         <v>46257</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="1">
@@ -3578,10 +3611,10 @@
       <c r="A101" s="1">
         <v>24</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101" s="3">
         <v>46258</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D101" s="1">
@@ -3609,10 +3642,10 @@
       <c r="A102" s="1">
         <v>25</v>
       </c>
-      <c r="B102" s="6">
+      <c r="B102" s="3">
         <v>46259</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="1">
@@ -3640,10 +3673,10 @@
       <c r="A103" s="1">
         <v>26</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="3">
         <v>46260</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D103" s="1">
@@ -3671,10 +3704,10 @@
       <c r="A104" s="1">
         <v>27</v>
       </c>
-      <c r="B104" s="6">
+      <c r="B104" s="3">
         <v>46261</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D104" s="1">
@@ -3702,10 +3735,10 @@
       <c r="A105" s="1">
         <v>28</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="3">
         <v>46262</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D105" s="1">
@@ -3733,10 +3766,10 @@
       <c r="A106" s="1">
         <v>29</v>
       </c>
-      <c r="B106" s="6">
+      <c r="B106" s="3">
         <v>46263</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="1">
@@ -3764,10 +3797,10 @@
       <c r="A107" s="1">
         <v>30</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="3">
         <v>46264</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="1">
@@ -3795,10 +3828,10 @@
       <c r="A108" s="1">
         <v>30</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B108" s="3">
         <v>46265</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D108" s="1">
@@ -3824,6 +3857,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -3833,24 +3884,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839DDFEF-FE8E-4D7E-B7EA-72F916047331}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7C01E-96B7-40E3-AFB8-D89B19C0BF0F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,23 +779,34 @@
       <c r="D9" s="1">
         <v>45</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <f>65.1+16</f>
+        <v>81.099999999999994</v>
+      </c>
       <c r="F9" s="1">
         <v>35.1</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>34.5</v>
+      </c>
       <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>60.9</v>
+      </c>
       <c r="J9" s="1">
         <v>12</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <v>26</v>
+      </c>
       <c r="L9" s="1">
         <v>13.5</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1">
+        <v>28.1</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1744,7 +1755,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="F42" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G42" s="1">
         <v>13</v>
@@ -1785,7 +1796,7 @@
         <v>20.2</v>
       </c>
       <c r="F43" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G43" s="1">
         <v>13.1</v>
@@ -1826,7 +1837,7 @@
         <v>20.2</v>
       </c>
       <c r="F44" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G44" s="1">
         <v>13.1</v>
@@ -1868,7 +1879,7 @@
         <v>29.7</v>
       </c>
       <c r="F45" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
         <v>10.9</v>
@@ -1905,23 +1916,33 @@
       <c r="D46" s="1">
         <v>15</v>
       </c>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1">
+        <v>22.9</v>
+      </c>
       <c r="F46" s="1">
-        <v>15</v>
-      </c>
-      <c r="G46" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G46" s="1">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="H46" s="1">
         <v>7.4</v>
       </c>
-      <c r="I46" s="1"/>
+      <c r="I46" s="1">
+        <v>21.1</v>
+      </c>
       <c r="J46" s="1">
         <v>8</v>
       </c>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1">
+        <v>10.9</v>
+      </c>
       <c r="L46" s="1">
         <v>2.8</v>
       </c>
-      <c r="M46" s="1"/>
+      <c r="M46" s="1">
+        <v>9.1999999999999993</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
@@ -1938,7 +1959,7 @@
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1">
@@ -1969,7 +1990,7 @@
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1">
@@ -2000,7 +2021,7 @@
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1">
@@ -2031,7 +2052,7 @@
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1">
@@ -2062,7 +2083,7 @@
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1">
@@ -2093,7 +2114,7 @@
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1">
@@ -2124,7 +2145,7 @@
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1">
@@ -2155,7 +2176,7 @@
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1">
@@ -2186,7 +2207,7 @@
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1">
@@ -2217,7 +2238,7 @@
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1">
@@ -2248,7 +2269,7 @@
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1">
@@ -2279,7 +2300,7 @@
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1">
@@ -2310,7 +2331,7 @@
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1">
@@ -2341,7 +2362,7 @@
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
@@ -2372,7 +2393,7 @@
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1">
@@ -2403,7 +2424,7 @@
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1">
@@ -2434,7 +2455,7 @@
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1">
@@ -2465,7 +2486,7 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1">
@@ -2496,7 +2517,7 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1">
@@ -2527,7 +2548,7 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1">
@@ -2558,7 +2579,7 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1">
@@ -2589,7 +2610,7 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1">
@@ -2620,7 +2641,7 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1">
@@ -2651,7 +2672,7 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1">
@@ -2682,7 +2703,7 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1">
@@ -2713,7 +2734,7 @@
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1">
@@ -3031,23 +3052,34 @@
       <c r="D82" s="1">
         <v>22</v>
       </c>
-      <c r="E82" s="1"/>
+      <c r="E82" s="1">
+        <f>28.8+15.8</f>
+        <v>44.6</v>
+      </c>
       <c r="F82" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="H82" s="1">
         <v>3.7</v>
       </c>
-      <c r="I82" s="1"/>
+      <c r="I82" s="1">
+        <v>12.4</v>
+      </c>
       <c r="J82" s="1">
         <v>5</v>
       </c>
-      <c r="K82" s="1"/>
+      <c r="K82" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L82" s="1">
         <v>2.7</v>
       </c>
-      <c r="M82" s="1"/>
+      <c r="M82" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7C01E-96B7-40E3-AFB8-D89B19C0BF0F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8298F96-C50C-4344-B252-CA791528A761}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -821,23 +821,34 @@
       <c r="D10" s="1">
         <v>45</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1">
+        <f>54.2+17.5+14.7</f>
+        <v>86.4</v>
+      </c>
       <c r="F10" s="1">
         <v>35.1</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>48</v>
+      </c>
       <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>64.400000000000006</v>
+      </c>
       <c r="J10" s="1">
         <v>12</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <v>22.3</v>
+      </c>
       <c r="L10" s="1">
         <v>13.5</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1615,21 +1626,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1673,13 +1684,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1704,9 +1715,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -1957,23 +1968,34 @@
       <c r="D47" s="1">
         <v>15</v>
       </c>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1">
+        <f>16.4+14.9</f>
+        <v>31.299999999999997</v>
+      </c>
       <c r="F47" s="1">
         <v>10</v>
       </c>
-      <c r="G47" s="1"/>
+      <c r="G47" s="1">
+        <v>13.1</v>
+      </c>
       <c r="H47" s="1">
         <v>7.4</v>
       </c>
-      <c r="I47" s="1"/>
+      <c r="I47" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="J47" s="1">
         <v>8</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1">
+        <v>10</v>
+      </c>
       <c r="L47" s="1">
         <v>2.8</v>
       </c>
-      <c r="M47" s="1"/>
+      <c r="M47" s="1">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
@@ -2751,21 +2773,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2809,13 +2831,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2840,9 +2862,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3094,23 +3116,34 @@
       <c r="D83" s="1">
         <v>22</v>
       </c>
-      <c r="E83" s="1"/>
+      <c r="E83" s="1">
+        <f>35.6</f>
+        <v>35.6</v>
+      </c>
       <c r="F83" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1">
+        <v>13.2</v>
+      </c>
       <c r="H83" s="1">
         <v>3.7</v>
       </c>
-      <c r="I83" s="1"/>
+      <c r="I83" s="1">
+        <v>11.7</v>
+      </c>
       <c r="J83" s="1">
         <v>5</v>
       </c>
-      <c r="K83" s="1"/>
+      <c r="K83" s="1">
+        <v>9.6</v>
+      </c>
       <c r="L83" s="1">
         <v>2.7</v>
       </c>
-      <c r="M83" s="1"/>
+      <c r="M83" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
@@ -3889,6 +3922,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -3898,24 +3949,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8298F96-C50C-4344-B252-CA791528A761}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C283CA-0F13-45ED-83E7-DB373CB78198}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -863,23 +863,34 @@
       <c r="D11" s="1">
         <v>45</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1">
+        <f>58.1+35</f>
+        <v>93.1</v>
+      </c>
       <c r="F11" s="1">
         <v>35.1</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>54.4</v>
+      </c>
       <c r="H11" s="1">
         <v>30</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>73.7</v>
+      </c>
       <c r="J11" s="1">
         <v>12</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <v>25.7</v>
+      </c>
       <c r="L11" s="1">
         <v>13.5</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1">
+        <v>27.1</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1626,21 +1637,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1684,13 +1695,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1715,9 +1726,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2010,23 +2021,33 @@
       <c r="D48" s="1">
         <v>15</v>
       </c>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1">
+        <v>25.9</v>
+      </c>
       <c r="F48" s="1">
         <v>10</v>
       </c>
-      <c r="G48" s="1"/>
+      <c r="G48" s="1">
+        <v>13.5</v>
+      </c>
       <c r="H48" s="1">
         <v>7.4</v>
       </c>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1">
+        <v>18.100000000000001</v>
+      </c>
       <c r="J48" s="1">
         <v>8</v>
       </c>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="L48" s="1">
         <v>2.8</v>
       </c>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
@@ -2773,21 +2794,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2831,13 +2852,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2862,9 +2883,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3158,23 +3179,34 @@
       <c r="D84" s="1">
         <v>22</v>
       </c>
-      <c r="E84" s="1"/>
+      <c r="E84" s="1">
+        <f>26.3+20</f>
+        <v>46.3</v>
+      </c>
       <c r="F84" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G84" s="1"/>
+      <c r="G84" s="1">
+        <v>11.4</v>
+      </c>
       <c r="H84" s="1">
         <v>3.7</v>
       </c>
-      <c r="I84" s="1"/>
+      <c r="I84" s="1">
+        <v>10.5</v>
+      </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
-      <c r="K84" s="1"/>
+      <c r="K84" s="1">
+        <v>9</v>
+      </c>
       <c r="L84" s="1">
         <v>2.7</v>
       </c>
-      <c r="M84" s="1"/>
+      <c r="M84" s="1">
+        <v>10.199999999999999</v>
+      </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
@@ -3922,6 +3954,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -3931,24 +3981,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C283CA-0F13-45ED-83E7-DB373CB78198}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC5E9B8-D525-4D1F-B36F-2944D76D8655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -905,23 +905,33 @@
       <c r="D12" s="1">
         <v>45</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>52</v>
+      </c>
       <c r="F12" s="1">
         <v>35.1</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>48.6</v>
+      </c>
       <c r="H12" s="1">
         <v>30</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>67.3</v>
+      </c>
       <c r="J12" s="1">
         <v>12</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <v>27.6</v>
+      </c>
       <c r="L12" s="1">
         <v>13.5</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1">
+        <v>33.200000000000003</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -936,23 +946,33 @@
       <c r="D13" s="1">
         <v>45</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <v>54.5</v>
+      </c>
       <c r="F13" s="1">
         <v>35.1</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>49</v>
+      </c>
       <c r="H13" s="1">
         <v>30</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>67.3</v>
+      </c>
       <c r="J13" s="1">
         <v>12</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <v>32</v>
+      </c>
       <c r="L13" s="1">
         <v>13.5</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1">
+        <v>33.200000000000003</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -967,23 +987,34 @@
       <c r="D14" s="1">
         <v>45</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <f>54.5+52.1</f>
+        <v>106.6</v>
+      </c>
       <c r="F14" s="1">
         <v>35.1</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>49</v>
+      </c>
       <c r="H14" s="1">
         <v>30</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>67.3</v>
+      </c>
       <c r="J14" s="1">
         <v>12</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1">
+        <v>32.1</v>
+      </c>
       <c r="L14" s="1">
         <v>13.5</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1">
+        <v>33.200000000000003</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1637,21 +1668,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1695,13 +1726,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1726,9 +1757,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2062,23 +2093,33 @@
       <c r="D49" s="1">
         <v>15</v>
       </c>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1">
+        <v>21.4</v>
+      </c>
       <c r="F49" s="1">
         <v>10</v>
       </c>
-      <c r="G49" s="1"/>
+      <c r="G49" s="1">
+        <v>24.6</v>
+      </c>
       <c r="H49" s="1">
         <v>7.4</v>
       </c>
-      <c r="I49" s="1"/>
+      <c r="I49" s="1">
+        <v>16.5</v>
+      </c>
       <c r="J49" s="1">
         <v>8</v>
       </c>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1">
+        <v>8.5</v>
+      </c>
       <c r="L49" s="1">
         <v>2.8</v>
       </c>
-      <c r="M49" s="1"/>
+      <c r="M49" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
@@ -2093,23 +2134,33 @@
       <c r="D50" s="1">
         <v>15</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1">
+        <v>21.8</v>
+      </c>
       <c r="F50" s="1">
         <v>10</v>
       </c>
-      <c r="G50" s="1"/>
+      <c r="G50" s="1">
+        <v>25</v>
+      </c>
       <c r="H50" s="1">
         <v>7.4</v>
       </c>
-      <c r="I50" s="1"/>
+      <c r="I50" s="1">
+        <v>16.5</v>
+      </c>
       <c r="J50" s="1">
         <v>8</v>
       </c>
-      <c r="K50" s="1"/>
+      <c r="K50" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="L50" s="1">
         <v>2.8</v>
       </c>
-      <c r="M50" s="1"/>
+      <c r="M50" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
@@ -2124,23 +2175,34 @@
       <c r="D51" s="1">
         <v>15</v>
       </c>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1">
+        <f>21.8</f>
+        <v>21.8</v>
+      </c>
       <c r="F51" s="1">
         <v>10</v>
       </c>
-      <c r="G51" s="1"/>
+      <c r="G51" s="1">
+        <v>25</v>
+      </c>
       <c r="H51" s="1">
         <v>7.4</v>
       </c>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <v>16.5</v>
+      </c>
       <c r="J51" s="1">
         <v>8</v>
       </c>
-      <c r="K51" s="1"/>
+      <c r="K51" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="L51" s="1">
         <v>2.8</v>
       </c>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -2794,21 +2856,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2852,13 +2914,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2883,9 +2945,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3221,23 +3283,33 @@
       <c r="D85" s="1">
         <v>22</v>
       </c>
-      <c r="E85" s="1"/>
+      <c r="E85" s="1">
+        <v>38.799999999999997</v>
+      </c>
       <c r="F85" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G85" s="1"/>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
       <c r="H85" s="1">
         <v>3.7</v>
       </c>
-      <c r="I85" s="1"/>
+      <c r="I85" s="1">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
-      <c r="K85" s="1"/>
+      <c r="K85" s="1">
+        <v>7.9</v>
+      </c>
       <c r="L85" s="1">
         <v>2.7</v>
       </c>
-      <c r="M85" s="1"/>
+      <c r="M85" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
@@ -3252,23 +3324,33 @@
       <c r="D86" s="1">
         <v>22</v>
       </c>
-      <c r="E86" s="1"/>
+      <c r="E86" s="1">
+        <v>39.200000000000003</v>
+      </c>
       <c r="F86" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G86" s="1"/>
+      <c r="G86" s="1">
+        <v>10.1</v>
+      </c>
       <c r="H86" s="1">
         <v>3.7</v>
       </c>
-      <c r="I86" s="1"/>
+      <c r="I86" s="1">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
-      <c r="K86" s="1"/>
+      <c r="K86" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L86" s="1">
         <v>2.7</v>
       </c>
-      <c r="M86" s="1"/>
+      <c r="M86" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
@@ -3283,23 +3365,34 @@
       <c r="D87" s="1">
         <v>22</v>
       </c>
-      <c r="E87" s="1"/>
+      <c r="E87" s="1">
+        <f>39.2</f>
+        <v>39.200000000000003</v>
+      </c>
       <c r="F87" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G87" s="1"/>
+      <c r="G87" s="1">
+        <v>10.1</v>
+      </c>
       <c r="H87" s="1">
         <v>3.7</v>
       </c>
-      <c r="I87" s="1"/>
+      <c r="I87" s="1">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="J87" s="1">
         <v>5</v>
       </c>
-      <c r="K87" s="1"/>
+      <c r="K87" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L87" s="1">
         <v>2.7</v>
       </c>
-      <c r="M87" s="1"/>
+      <c r="M87" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
@@ -3954,6 +4047,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -3963,24 +4074,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC5E9B8-D525-4D1F-B36F-2944D76D8655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D5364-CC9C-4187-B085-2C65E18E057A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1029,23 +1029,34 @@
       <c r="D15" s="1">
         <v>45</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <f>75.2+35</f>
+        <v>110.2</v>
+      </c>
       <c r="F15" s="1">
         <v>35.1</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>51.3</v>
+      </c>
       <c r="H15" s="1">
         <v>30</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>57</v>
+      </c>
       <c r="J15" s="1">
         <v>12</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1">
+        <v>27.6</v>
+      </c>
       <c r="L15" s="1">
         <v>13.5</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1">
+        <v>30.7</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1668,21 +1679,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1726,13 +1737,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1757,9 +1768,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2217,23 +2228,33 @@
       <c r="D52" s="1">
         <v>15</v>
       </c>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1">
+        <v>15.7</v>
+      </c>
       <c r="F52" s="1">
         <v>10</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1">
+        <v>23.2</v>
+      </c>
       <c r="H52" s="1">
         <v>7.4</v>
       </c>
-      <c r="I52" s="1"/>
+      <c r="I52" s="1">
+        <v>14</v>
+      </c>
       <c r="J52" s="1">
         <v>8</v>
       </c>
-      <c r="K52" s="1"/>
+      <c r="K52" s="1">
+        <v>7.9</v>
+      </c>
       <c r="L52" s="1">
         <v>2.8</v>
       </c>
-      <c r="M52" s="1"/>
+      <c r="M52" s="1">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -2856,21 +2877,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2914,13 +2935,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2945,9 +2966,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3407,23 +3428,34 @@
       <c r="D88" s="1">
         <v>22</v>
       </c>
-      <c r="E88" s="1"/>
+      <c r="E88" s="1">
+        <f>25.2+16.7</f>
+        <v>41.9</v>
+      </c>
       <c r="F88" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G88" s="1"/>
+      <c r="G88" s="1">
+        <v>7.7</v>
+      </c>
       <c r="H88" s="1">
         <v>3.7</v>
       </c>
-      <c r="I88" s="1"/>
+      <c r="I88" s="1">
+        <v>6</v>
+      </c>
       <c r="J88" s="1">
         <v>5</v>
       </c>
-      <c r="K88" s="1"/>
+      <c r="K88" s="1">
+        <v>12.2</v>
+      </c>
       <c r="L88" s="1">
         <v>2.7</v>
       </c>
-      <c r="M88" s="1"/>
+      <c r="M88" s="1">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
@@ -4047,6 +4079,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4056,24 +4106,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D5364-CC9C-4187-B085-2C65E18E057A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07866376-8BD0-4705-B14C-84BFAFCC6B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1071,23 +1071,34 @@
       <c r="D16" s="1">
         <v>45</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1">
+        <f>76+16.1</f>
+        <v>92.1</v>
+      </c>
       <c r="F16" s="1">
         <v>35.1</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>57.8</v>
+      </c>
       <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>57.2</v>
+      </c>
       <c r="J16" s="1">
         <v>12</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1">
+        <v>23.8</v>
+      </c>
       <c r="L16" s="1">
         <v>13.5</v>
       </c>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1679,21 +1690,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1737,13 +1748,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1768,9 +1779,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2269,23 +2280,34 @@
       <c r="D53" s="1">
         <v>15</v>
       </c>
-      <c r="E53" s="1"/>
+      <c r="E53" s="1">
+        <f>7.7+14</f>
+        <v>21.7</v>
+      </c>
       <c r="F53" s="1">
         <v>10</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>20.9</v>
+      </c>
       <c r="H53" s="1">
         <v>7.4</v>
       </c>
-      <c r="I53" s="1"/>
+      <c r="I53" s="1">
+        <v>11.7</v>
+      </c>
       <c r="J53" s="1">
         <v>8</v>
       </c>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1">
+        <v>15.8</v>
+      </c>
       <c r="L53" s="1">
         <v>2.8</v>
       </c>
-      <c r="M53" s="1"/>
+      <c r="M53" s="1">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -2877,21 +2899,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2935,13 +2957,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2966,9 +2988,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3470,23 +3492,34 @@
       <c r="D89" s="1">
         <v>22</v>
       </c>
-      <c r="E89" s="1"/>
+      <c r="E89" s="1">
+        <f>31.2+10</f>
+        <v>41.2</v>
+      </c>
       <c r="F89" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G89" s="1"/>
+      <c r="G89" s="1">
+        <v>12.5</v>
+      </c>
       <c r="H89" s="1">
         <v>3.7</v>
       </c>
-      <c r="I89" s="1"/>
+      <c r="I89" s="1">
+        <v>13.7</v>
+      </c>
       <c r="J89" s="1">
         <v>5</v>
       </c>
-      <c r="K89" s="1"/>
+      <c r="K89" s="1">
+        <v>14.2</v>
+      </c>
       <c r="L89" s="1">
         <v>2.7</v>
       </c>
-      <c r="M89" s="1"/>
+      <c r="M89" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
@@ -4079,6 +4112,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4088,24 +4139,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07866376-8BD0-4705-B14C-84BFAFCC6B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FD4F80-8F4D-434F-800F-D8B6CD7A5A0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1113,23 +1113,34 @@
       <c r="D17" s="1">
         <v>45</v>
       </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="1">
+        <f>65.8+35</f>
+        <v>100.8</v>
+      </c>
       <c r="F17" s="1">
         <v>35.1</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>54.6</v>
+      </c>
       <c r="H17" s="1">
         <v>30</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>50.3</v>
+      </c>
       <c r="J17" s="1">
         <v>12</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <v>21.1</v>
+      </c>
       <c r="L17" s="1">
         <v>13.5</v>
       </c>
-      <c r="M17" s="1"/>
+      <c r="M17" s="1">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1690,21 +1701,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1748,13 +1759,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1779,9 +1790,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2322,23 +2333,33 @@
       <c r="D54" s="1">
         <v>15</v>
       </c>
-      <c r="E54" s="1"/>
+      <c r="E54" s="1">
+        <v>15.4</v>
+      </c>
       <c r="F54" s="1">
         <v>10</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1">
+        <v>28.3</v>
+      </c>
       <c r="H54" s="1">
         <v>7.4</v>
       </c>
-      <c r="I54" s="1"/>
+      <c r="I54" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="J54" s="1">
         <v>8</v>
       </c>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1">
+        <v>15.6</v>
+      </c>
       <c r="L54" s="1">
         <v>2.8</v>
       </c>
-      <c r="M54" s="1"/>
+      <c r="M54" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2899,21 +2920,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2957,13 +2978,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2988,9 +3009,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3534,23 +3555,34 @@
       <c r="D90" s="1">
         <v>22</v>
       </c>
-      <c r="E90" s="1"/>
+      <c r="E90" s="1">
+        <f>33.4+2</f>
+        <v>35.4</v>
+      </c>
       <c r="F90" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G90" s="1"/>
+      <c r="G90" s="1">
+        <v>14</v>
+      </c>
       <c r="H90" s="1">
         <v>3.7</v>
       </c>
-      <c r="I90" s="1"/>
+      <c r="I90" s="1">
+        <v>13.1</v>
+      </c>
       <c r="J90" s="1">
         <v>5</v>
       </c>
-      <c r="K90" s="1"/>
+      <c r="K90" s="1">
+        <v>12.2</v>
+      </c>
       <c r="L90" s="1">
         <v>2.7</v>
       </c>
-      <c r="M90" s="1"/>
+      <c r="M90" s="1">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -4112,6 +4144,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4121,24 +4171,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FD4F80-8F4D-434F-800F-D8B6CD7A5A0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EB6ACD-B7C6-437B-8F0B-7D320E37D75B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,23 +1155,34 @@
       <c r="D18" s="1">
         <v>45</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <f>74.4+35</f>
+        <v>109.4</v>
+      </c>
       <c r="F18" s="1">
         <v>35.1</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>55.6</v>
+      </c>
       <c r="H18" s="1">
         <v>30</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>57.9</v>
+      </c>
       <c r="J18" s="1">
         <v>12</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1">
+        <v>19</v>
+      </c>
       <c r="L18" s="1">
         <v>13.5</v>
       </c>
-      <c r="M18" s="1"/>
+      <c r="M18" s="1">
+        <v>19.600000000000001</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -2374,23 +2385,34 @@
       <c r="D55" s="1">
         <v>15</v>
       </c>
-      <c r="E55" s="1"/>
+      <c r="E55" s="1">
+        <f>8.7+14</f>
+        <v>22.7</v>
+      </c>
       <c r="F55" s="1">
         <v>10</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1">
+        <v>26</v>
+      </c>
       <c r="H55" s="1">
         <v>7.4</v>
       </c>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1">
+        <v>8.4</v>
+      </c>
       <c r="J55" s="1">
         <v>8</v>
       </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1">
+        <v>14.3</v>
+      </c>
       <c r="L55" s="1">
         <v>2.8</v>
       </c>
-      <c r="M55" s="1"/>
+      <c r="M55" s="1">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -3597,23 +3619,34 @@
       <c r="D91" s="1">
         <v>22</v>
       </c>
-      <c r="E91" s="1"/>
+      <c r="E91" s="1">
+        <f>23+13</f>
+        <v>36</v>
+      </c>
       <c r="F91" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1">
+        <v>12</v>
+      </c>
       <c r="H91" s="1">
         <v>3.7</v>
       </c>
-      <c r="I91" s="1"/>
+      <c r="I91" s="1">
+        <v>11.5</v>
+      </c>
       <c r="J91" s="1">
         <v>5</v>
       </c>
-      <c r="K91" s="1"/>
+      <c r="K91" s="1">
+        <v>11.4</v>
+      </c>
       <c r="L91" s="1">
         <v>2.7</v>
       </c>
-      <c r="M91" s="1"/>
+      <c r="M91" s="1">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EB6ACD-B7C6-437B-8F0B-7D320E37D75B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51419EC4-00A8-4F5C-99C8-987C72ABCB32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1197,23 +1197,33 @@
       <c r="D19" s="1">
         <v>45</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1">
+        <v>86.2</v>
+      </c>
       <c r="F19" s="1">
         <v>35.1</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>46.4</v>
+      </c>
       <c r="H19" s="1">
         <v>30</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>50</v>
+      </c>
       <c r="J19" s="1">
         <v>12</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1">
+        <v>16.5</v>
+      </c>
       <c r="L19" s="1">
         <v>13.5</v>
       </c>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1">
+        <v>17.899999999999999</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1228,23 +1238,33 @@
       <c r="D20" s="1">
         <v>45</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1">
+        <v>87.3</v>
+      </c>
       <c r="F20" s="1">
         <v>35.1</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>46.5</v>
+      </c>
       <c r="H20" s="1">
         <v>30</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <v>50</v>
+      </c>
       <c r="J20" s="1">
         <v>12</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1">
+        <v>16.5</v>
+      </c>
       <c r="L20" s="1">
         <v>13.5</v>
       </c>
-      <c r="M20" s="1"/>
+      <c r="M20" s="1">
+        <v>17.899999999999999</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1259,23 +1279,33 @@
       <c r="D21" s="1">
         <v>45</v>
       </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1">
+        <v>122.1</v>
+      </c>
       <c r="F21" s="1">
         <v>35.1</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>46.5</v>
+      </c>
       <c r="H21" s="1">
         <v>30</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <v>50</v>
+      </c>
       <c r="J21" s="1">
         <v>12</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1">
+        <v>16.5</v>
+      </c>
       <c r="L21" s="1">
         <v>13.5</v>
       </c>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1">
+        <v>17.899999999999999</v>
+      </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1712,21 +1742,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1770,13 +1800,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1801,9 +1831,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2427,23 +2457,33 @@
       <c r="D56" s="1">
         <v>15</v>
       </c>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1">
+        <v>17.7</v>
+      </c>
       <c r="F56" s="1">
         <v>10</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1">
+        <v>23.4</v>
+      </c>
       <c r="H56" s="1">
         <v>7.4</v>
       </c>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J56" s="1">
         <v>8</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1">
+        <v>13.1</v>
+      </c>
       <c r="L56" s="1">
         <v>2.8</v>
       </c>
-      <c r="M56" s="1"/>
+      <c r="M56" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
@@ -2458,23 +2498,33 @@
       <c r="D57" s="1">
         <v>15</v>
       </c>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1">
+        <v>18.2</v>
+      </c>
       <c r="F57" s="1">
         <v>10</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1">
+        <v>23.4</v>
+      </c>
       <c r="H57" s="1">
         <v>7.4</v>
       </c>
-      <c r="I57" s="1"/>
+      <c r="I57" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J57" s="1">
         <v>8</v>
       </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1">
+        <v>13.1</v>
+      </c>
       <c r="L57" s="1">
         <v>2.8</v>
       </c>
-      <c r="M57" s="1"/>
+      <c r="M57" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -2489,23 +2539,33 @@
       <c r="D58" s="1">
         <v>15</v>
       </c>
-      <c r="E58" s="1"/>
+      <c r="E58" s="1">
+        <v>18.2</v>
+      </c>
       <c r="F58" s="1">
         <v>10</v>
       </c>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1">
+        <v>23.4</v>
+      </c>
       <c r="H58" s="1">
         <v>7.4</v>
       </c>
-      <c r="I58" s="1"/>
+      <c r="I58" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J58" s="1">
         <v>8</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1">
+        <v>13.1</v>
+      </c>
       <c r="L58" s="1">
         <v>2.8</v>
       </c>
-      <c r="M58" s="1"/>
+      <c r="M58" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
@@ -2942,21 +3002,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3000,13 +3060,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3031,9 +3091,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3661,23 +3721,33 @@
       <c r="D92" s="1">
         <v>22</v>
       </c>
-      <c r="E92" s="1"/>
+      <c r="E92" s="1">
+        <v>27.1</v>
+      </c>
       <c r="F92" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G92" s="1"/>
+      <c r="G92" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H92" s="1">
         <v>3.7</v>
       </c>
-      <c r="I92" s="1"/>
+      <c r="I92" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="J92" s="1">
         <v>5</v>
       </c>
-      <c r="K92" s="1"/>
+      <c r="K92" s="1">
+        <v>9.4</v>
+      </c>
       <c r="L92" s="1">
         <v>2.7</v>
       </c>
-      <c r="M92" s="1"/>
+      <c r="M92" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
@@ -3692,23 +3762,33 @@
       <c r="D93" s="1">
         <v>22</v>
       </c>
-      <c r="E93" s="1"/>
+      <c r="E93" s="1">
+        <v>27.6</v>
+      </c>
       <c r="F93" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G93" s="1"/>
+      <c r="G93" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H93" s="1">
         <v>3.7</v>
       </c>
-      <c r="I93" s="1"/>
+      <c r="I93" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
-      <c r="K93" s="1"/>
+      <c r="K93" s="1">
+        <v>9.5</v>
+      </c>
       <c r="L93" s="1">
         <v>2.7</v>
       </c>
-      <c r="M93" s="1"/>
+      <c r="M93" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
@@ -3723,23 +3803,33 @@
       <c r="D94" s="1">
         <v>22</v>
       </c>
-      <c r="E94" s="1"/>
+      <c r="E94" s="1">
+        <v>48</v>
+      </c>
       <c r="F94" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G94" s="1"/>
+      <c r="G94" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H94" s="1">
         <v>3.7</v>
       </c>
-      <c r="I94" s="1"/>
+      <c r="I94" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="J94" s="1">
         <v>5</v>
       </c>
-      <c r="K94" s="1"/>
+      <c r="K94" s="1">
+        <v>9.5</v>
+      </c>
       <c r="L94" s="1">
         <v>2.7</v>
       </c>
-      <c r="M94" s="1"/>
+      <c r="M94" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -4177,6 +4267,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4186,24 +4294,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51419EC4-00A8-4F5C-99C8-987C72ABCB32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C30247-B03D-4742-B96F-2C5555655ABA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1320,23 +1320,34 @@
       <c r="D22" s="1">
         <v>45</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1">
+        <f>92.2+17.2</f>
+        <v>109.4</v>
+      </c>
       <c r="F22" s="1">
         <v>35.1</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>34.4</v>
+      </c>
       <c r="H22" s="1">
         <v>30</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <v>48.1</v>
+      </c>
       <c r="J22" s="1">
         <v>12</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1">
+        <v>20.2</v>
+      </c>
       <c r="L22" s="1">
         <v>13.5</v>
       </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1742,21 +1753,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1800,13 +1811,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1831,9 +1842,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2580,23 +2591,33 @@
       <c r="D59" s="1">
         <v>15</v>
       </c>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1">
+        <v>10.8</v>
+      </c>
       <c r="F59" s="1">
         <v>10</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1">
+        <v>20.8</v>
+      </c>
       <c r="H59" s="1">
         <v>7.4</v>
       </c>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1">
+        <v>4.8</v>
+      </c>
       <c r="J59" s="1">
         <v>8</v>
       </c>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1">
+        <v>12.5</v>
+      </c>
       <c r="L59" s="1">
         <v>2.8</v>
       </c>
-      <c r="M59" s="1"/>
+      <c r="M59" s="1">
+        <v>10.1</v>
+      </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
@@ -3002,21 +3023,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3060,13 +3081,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3091,9 +3112,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3844,23 +3865,33 @@
       <c r="D95" s="1">
         <v>22</v>
       </c>
-      <c r="E95" s="1"/>
+      <c r="E95" s="1">
+        <v>36.5</v>
+      </c>
       <c r="F95" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G95" s="1"/>
+      <c r="G95" s="1">
+        <v>10.5</v>
+      </c>
       <c r="H95" s="1">
         <v>3.7</v>
       </c>
-      <c r="I95" s="1"/>
+      <c r="I95" s="1">
+        <v>6.3</v>
+      </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
-      <c r="K95" s="1"/>
+      <c r="K95" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="L95" s="1">
         <v>2.7</v>
       </c>
-      <c r="M95" s="1"/>
+      <c r="M95" s="1">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -4267,6 +4298,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4276,24 +4325,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C30247-B03D-4742-B96F-2C5555655ABA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEC4356-31CE-45EE-B71E-41B5816E1241}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1362,23 +1362,34 @@
       <c r="D23" s="1">
         <v>45</v>
       </c>
-      <c r="E23" s="1"/>
+      <c r="E23" s="1">
+        <f>79.9+16.3</f>
+        <v>96.2</v>
+      </c>
       <c r="F23" s="1">
         <v>35.1</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>45</v>
+      </c>
       <c r="H23" s="1">
         <v>30</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>41.2</v>
+      </c>
       <c r="J23" s="1">
         <v>12</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1">
+        <v>16.5</v>
+      </c>
       <c r="L23" s="1">
         <v>13.5</v>
       </c>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1">
+        <v>24.2</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1753,21 +1764,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1811,13 +1822,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1842,9 +1853,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2632,23 +2643,34 @@
       <c r="D60" s="1">
         <v>15</v>
       </c>
-      <c r="E60" s="1"/>
+      <c r="E60" s="1">
+        <f>3.3+14</f>
+        <v>17.3</v>
+      </c>
       <c r="F60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="H60" s="1">
         <v>7.4</v>
       </c>
-      <c r="I60" s="1"/>
+      <c r="I60" s="1">
+        <v>15.5</v>
+      </c>
       <c r="J60" s="1">
         <v>8</v>
       </c>
-      <c r="K60" s="1"/>
+      <c r="K60" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="L60" s="1">
         <v>2.8</v>
       </c>
-      <c r="M60" s="1"/>
+      <c r="M60" s="1">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
@@ -3023,21 +3045,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3081,13 +3103,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3112,9 +3134,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3906,23 +3928,34 @@
       <c r="D96" s="1">
         <v>22</v>
       </c>
-      <c r="E96" s="1"/>
+      <c r="E96" s="1">
+        <f>38.2+3.3</f>
+        <v>41.5</v>
+      </c>
       <c r="F96" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G96" s="1"/>
+      <c r="G96" s="1">
+        <v>11.3</v>
+      </c>
       <c r="H96" s="1">
         <v>3.7</v>
       </c>
-      <c r="I96" s="1"/>
+      <c r="I96" s="1">
+        <v>10.1</v>
+      </c>
       <c r="J96" s="1">
         <v>5</v>
       </c>
-      <c r="K96" s="1"/>
+      <c r="K96" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="L96" s="1">
         <v>2.7</v>
       </c>
-      <c r="M96" s="1"/>
+      <c r="M96" s="1">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -4298,6 +4331,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4307,24 +4358,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEC4356-31CE-45EE-B71E-41B5816E1241}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1475333-C3D7-44C1-9686-F982B8148D43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,23 +1404,34 @@
       <c r="D24" s="1">
         <v>45</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1">
+        <f>71.5+35-6.3</f>
+        <v>100.2</v>
+      </c>
       <c r="F24" s="1">
         <v>35.1</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>47.5</v>
+      </c>
       <c r="H24" s="1">
         <v>30</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>51.8</v>
+      </c>
       <c r="J24" s="1">
         <v>12</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="L24" s="1">
         <v>13.5</v>
       </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1">
+        <v>19.600000000000001</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -2685,23 +2696,34 @@
       <c r="D61" s="1">
         <v>15</v>
       </c>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1">
+        <f>13.7+14</f>
+        <v>27.7</v>
+      </c>
       <c r="F61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1">
+        <v>15.3</v>
+      </c>
       <c r="H61" s="1">
         <v>7.4</v>
       </c>
-      <c r="I61" s="1"/>
+      <c r="I61" s="1">
+        <v>14</v>
+      </c>
       <c r="J61" s="1">
         <v>8</v>
       </c>
-      <c r="K61" s="1"/>
+      <c r="K61" s="1">
+        <v>9.1</v>
+      </c>
       <c r="L61" s="1">
         <v>2.8</v>
       </c>
-      <c r="M61" s="1"/>
+      <c r="M61" s="1">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
@@ -3970,23 +3992,34 @@
       <c r="D97" s="1">
         <v>22</v>
       </c>
-      <c r="E97" s="1"/>
+      <c r="E97" s="1">
+        <f>33.7+8</f>
+        <v>41.7</v>
+      </c>
       <c r="F97" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G97" s="1"/>
+      <c r="G97" s="1">
+        <v>10.9</v>
+      </c>
       <c r="H97" s="1">
         <v>3.7</v>
       </c>
-      <c r="I97" s="1"/>
+      <c r="I97" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="J97" s="1">
         <v>5</v>
       </c>
-      <c r="K97" s="1"/>
+      <c r="K97" s="1">
+        <v>7.1</v>
+      </c>
       <c r="L97" s="1">
         <v>2.7</v>
       </c>
-      <c r="M97" s="1"/>
+      <c r="M97" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1475333-C3D7-44C1-9686-F982B8148D43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD70D01A-A564-4FF1-BD1D-4DF70BD75AB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1446,23 +1446,34 @@
       <c r="D25" s="1">
         <v>45</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1">
+        <f>78+17</f>
+        <v>95</v>
+      </c>
       <c r="F25" s="1">
         <v>35.1</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>56.8</v>
+      </c>
       <c r="H25" s="1">
         <v>30</v>
       </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1">
+        <v>43.1</v>
+      </c>
       <c r="J25" s="1">
         <v>12</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1">
+        <v>12.8</v>
+      </c>
       <c r="L25" s="1">
         <v>13.5</v>
       </c>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1775,21 +1786,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1833,13 +1844,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1864,9 +1875,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2738,23 +2749,34 @@
       <c r="D62" s="1">
         <v>15</v>
       </c>
-      <c r="E62" s="1"/>
+      <c r="E62" s="1">
+        <f>7.7+14</f>
+        <v>21.7</v>
+      </c>
       <c r="F62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1">
+        <v>12</v>
+      </c>
       <c r="H62" s="1">
         <v>7.4</v>
       </c>
-      <c r="I62" s="1"/>
+      <c r="I62" s="1">
+        <v>12.2</v>
+      </c>
       <c r="J62" s="1">
         <v>8</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="1">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="L62" s="1">
         <v>2.8</v>
       </c>
-      <c r="M62" s="1"/>
+      <c r="M62" s="1">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -3067,21 +3089,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3125,13 +3147,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3156,9 +3178,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4034,23 +4056,34 @@
       <c r="D98" s="1">
         <v>22</v>
       </c>
-      <c r="E98" s="1"/>
+      <c r="E98" s="1">
+        <f>31.4+8</f>
+        <v>39.4</v>
+      </c>
       <c r="F98" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G98" s="1"/>
+      <c r="G98" s="1">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="H98" s="1">
         <v>3.7</v>
       </c>
-      <c r="I98" s="1"/>
+      <c r="I98" s="1">
+        <v>7.5</v>
+      </c>
       <c r="J98" s="1">
         <v>5</v>
       </c>
-      <c r="K98" s="1"/>
+      <c r="K98" s="1">
+        <v>6.2</v>
+      </c>
       <c r="L98" s="1">
         <v>2.7</v>
       </c>
-      <c r="M98" s="1"/>
+      <c r="M98" s="1">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -4364,6 +4397,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4373,24 +4424,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD70D01A-A564-4FF1-BD1D-4DF70BD75AB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1C8930-4476-4FB0-83B0-DFCCA46613E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1488,23 +1488,33 @@
       <c r="D26" s="1">
         <v>45</v>
       </c>
-      <c r="E26" s="1"/>
+      <c r="E26" s="1">
+        <v>52.8</v>
+      </c>
       <c r="F26" s="1">
         <v>35.1</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>49</v>
+      </c>
       <c r="H26" s="1">
         <v>30</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>37</v>
+      </c>
       <c r="J26" s="1">
         <v>12</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="L26" s="1">
         <v>13.5</v>
       </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1519,23 +1529,33 @@
       <c r="D27" s="1">
         <v>45</v>
       </c>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1">
+        <v>54.8</v>
+      </c>
       <c r="F27" s="1">
         <v>35.1</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>49.7</v>
+      </c>
       <c r="H27" s="1">
         <v>30</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>37</v>
+      </c>
       <c r="J27" s="1">
         <v>12</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="L27" s="1">
         <v>13.5</v>
       </c>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1550,23 +1570,34 @@
       <c r="D28" s="1">
         <v>45</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <f>54.8+52</f>
+        <v>106.8</v>
+      </c>
       <c r="F28" s="1">
         <v>35.1</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>49.7</v>
+      </c>
       <c r="H28" s="1">
         <v>30</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>37</v>
+      </c>
       <c r="J28" s="1">
         <v>12</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="L28" s="1">
         <v>13.5</v>
       </c>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1786,21 +1817,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1844,13 +1875,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1875,9 +1906,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2791,23 +2822,33 @@
       <c r="D63" s="1">
         <v>15</v>
       </c>
-      <c r="E63" s="1"/>
+      <c r="E63" s="1">
+        <v>16</v>
+      </c>
       <c r="F63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1">
+        <v>10.5</v>
+      </c>
       <c r="H63" s="1">
         <v>7.4</v>
       </c>
-      <c r="I63" s="1"/>
+      <c r="I63" s="1">
+        <v>22.2</v>
+      </c>
       <c r="J63" s="1">
         <v>8</v>
       </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="1">
+        <v>7.3</v>
+      </c>
       <c r="L63" s="1">
         <v>2.8</v>
       </c>
-      <c r="M63" s="1"/>
+      <c r="M63" s="1">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
@@ -2822,23 +2863,33 @@
       <c r="D64" s="1">
         <v>15</v>
       </c>
-      <c r="E64" s="1"/>
+      <c r="E64" s="1">
+        <v>16.899999999999999</v>
+      </c>
       <c r="F64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1">
+        <v>10.9</v>
+      </c>
       <c r="H64" s="1">
         <v>7.4</v>
       </c>
-      <c r="I64" s="1"/>
+      <c r="I64" s="1">
+        <v>22.2</v>
+      </c>
       <c r="J64" s="1">
         <v>8</v>
       </c>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1">
+        <v>7.3</v>
+      </c>
       <c r="L64" s="1">
         <v>2.8</v>
       </c>
-      <c r="M64" s="1"/>
+      <c r="M64" s="1">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -2853,23 +2904,33 @@
       <c r="D65" s="1">
         <v>15</v>
       </c>
-      <c r="E65" s="1"/>
+      <c r="E65" s="1">
+        <v>31.6</v>
+      </c>
       <c r="F65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>10.9</v>
+      </c>
       <c r="H65" s="1">
         <v>7.4</v>
       </c>
-      <c r="I65" s="1"/>
+      <c r="I65" s="1">
+        <v>22.2</v>
+      </c>
       <c r="J65" s="1">
         <v>8</v>
       </c>
-      <c r="K65" s="1"/>
+      <c r="K65" s="1">
+        <v>7.3</v>
+      </c>
       <c r="L65" s="1">
         <v>2.8</v>
       </c>
-      <c r="M65" s="1"/>
+      <c r="M65" s="1">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
@@ -3089,21 +3150,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3147,13 +3208,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3178,9 +3239,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4098,23 +4159,33 @@
       <c r="D99" s="1">
         <v>22</v>
       </c>
-      <c r="E99" s="1"/>
+      <c r="E99" s="1">
+        <v>32.700000000000003</v>
+      </c>
       <c r="F99" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G99" s="1"/>
+      <c r="G99" s="1">
+        <v>7.4</v>
+      </c>
       <c r="H99" s="1">
         <v>3.7</v>
       </c>
-      <c r="I99" s="1"/>
+      <c r="I99" s="1">
+        <v>6.4</v>
+      </c>
       <c r="J99" s="1">
         <v>5</v>
       </c>
-      <c r="K99" s="1"/>
+      <c r="K99" s="1">
+        <v>7</v>
+      </c>
       <c r="L99" s="1">
         <v>2.7</v>
       </c>
-      <c r="M99" s="1"/>
+      <c r="M99" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -4129,23 +4200,33 @@
       <c r="D100" s="1">
         <v>22</v>
       </c>
-      <c r="E100" s="1"/>
+      <c r="E100" s="1">
+        <v>33.200000000000003</v>
+      </c>
       <c r="F100" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G100" s="1"/>
+      <c r="G100" s="1">
+        <v>7.1</v>
+      </c>
       <c r="H100" s="1">
         <v>3.7</v>
       </c>
-      <c r="I100" s="1"/>
+      <c r="I100" s="1">
+        <v>6.4</v>
+      </c>
       <c r="J100" s="1">
         <v>5</v>
       </c>
-      <c r="K100" s="1"/>
+      <c r="K100" s="1">
+        <v>7</v>
+      </c>
       <c r="L100" s="1">
         <v>2.7</v>
       </c>
-      <c r="M100" s="1"/>
+      <c r="M100" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -4160,23 +4241,33 @@
       <c r="D101" s="1">
         <v>22</v>
       </c>
-      <c r="E101" s="1"/>
+      <c r="E101" s="1">
+        <v>39.9</v>
+      </c>
       <c r="F101" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G101" s="1"/>
+      <c r="G101" s="1">
+        <v>7.1</v>
+      </c>
       <c r="H101" s="1">
         <v>3.7</v>
       </c>
-      <c r="I101" s="1"/>
+      <c r="I101" s="1">
+        <v>6.4</v>
+      </c>
       <c r="J101" s="1">
         <v>5</v>
       </c>
-      <c r="K101" s="1"/>
+      <c r="K101" s="1">
+        <v>7</v>
+      </c>
       <c r="L101" s="1">
         <v>2.7</v>
       </c>
-      <c r="M101" s="1"/>
+      <c r="M101" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -4397,6 +4488,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4406,24 +4515,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1C8930-4476-4FB0-83B0-DFCCA46613E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E970168-CCE2-4559-9128-C9092CE44330}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1612,23 +1612,34 @@
       <c r="D29" s="1">
         <v>45</v>
       </c>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1">
+        <f>79.8+35</f>
+        <v>114.8</v>
+      </c>
       <c r="F29" s="1">
         <v>35.1</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>56.5</v>
+      </c>
       <c r="H29" s="1">
         <v>30</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>44.9</v>
+      </c>
       <c r="J29" s="1">
         <v>12</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1">
+        <v>15.6</v>
+      </c>
       <c r="L29" s="1">
         <v>13.5</v>
       </c>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -1817,21 +1828,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1875,13 +1886,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1906,9 +1917,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2945,23 +2956,34 @@
       <c r="D66" s="1">
         <v>15</v>
       </c>
-      <c r="E66" s="1"/>
+      <c r="E66" s="1">
+        <f>24.3+14</f>
+        <v>38.299999999999997</v>
+      </c>
       <c r="F66" s="1">
         <v>10</v>
       </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1">
+        <v>20.5</v>
+      </c>
       <c r="H66" s="1">
         <v>7.4</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1">
+        <v>20</v>
+      </c>
       <c r="J66" s="1">
         <v>8</v>
       </c>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1">
+        <v>6.5</v>
+      </c>
       <c r="L66" s="1">
         <v>2.8</v>
       </c>
-      <c r="M66" s="1"/>
+      <c r="M66" s="1">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
@@ -3150,21 +3172,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3208,13 +3230,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3239,9 +3261,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4282,23 +4304,34 @@
       <c r="D102" s="1">
         <v>22</v>
       </c>
-      <c r="E102" s="1"/>
+      <c r="E102" s="1">
+        <f>27.6+10</f>
+        <v>37.6</v>
+      </c>
       <c r="F102" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G102" s="1"/>
+      <c r="G102" s="1">
+        <v>5.6</v>
+      </c>
       <c r="H102" s="1">
         <v>3.7</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="1">
+        <v>3.7</v>
+      </c>
       <c r="J102" s="1">
         <v>5</v>
       </c>
-      <c r="K102" s="1"/>
+      <c r="K102" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L102" s="1">
         <v>2.7</v>
       </c>
-      <c r="M102" s="1"/>
+      <c r="M102" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -4488,6 +4521,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4497,24 +4548,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E970168-CCE2-4559-9128-C9092CE44330}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E13CDD6-EE86-40C2-9784-3157F6112557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1654,23 +1654,34 @@
       <c r="D30" s="1">
         <v>45</v>
       </c>
-      <c r="E30" s="1"/>
+      <c r="E30" s="1">
+        <f>99.7</f>
+        <v>99.7</v>
+      </c>
       <c r="F30" s="1">
         <v>35.1</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>46.7</v>
+      </c>
       <c r="H30" s="1">
         <v>30</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>46.6</v>
+      </c>
       <c r="J30" s="1">
         <v>12</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1">
+        <v>12.2</v>
+      </c>
       <c r="L30" s="1">
         <v>13.5</v>
       </c>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1">
+        <v>15.7</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2998,23 +3009,33 @@
       <c r="D67" s="1">
         <v>15</v>
       </c>
-      <c r="E67" s="1"/>
+      <c r="E67" s="1">
+        <v>27.3</v>
+      </c>
       <c r="F67" s="1">
         <v>10</v>
       </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1">
+        <v>18.899999999999999</v>
+      </c>
       <c r="H67" s="1">
         <v>7.4</v>
       </c>
-      <c r="I67" s="1"/>
+      <c r="I67" s="1">
+        <v>17.399999999999999</v>
+      </c>
       <c r="J67" s="1">
         <v>8</v>
       </c>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1">
+        <v>5.3</v>
+      </c>
       <c r="L67" s="1">
         <v>2.8</v>
       </c>
-      <c r="M67" s="1"/>
+      <c r="M67" s="1">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
@@ -4346,23 +4367,34 @@
       <c r="D103" s="1">
         <v>22</v>
       </c>
-      <c r="E103" s="1"/>
+      <c r="E103" s="1">
+        <f>49.9</f>
+        <v>49.9</v>
+      </c>
       <c r="F103" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G103" s="1"/>
+      <c r="G103" s="1">
+        <v>10.4</v>
+      </c>
       <c r="H103" s="1">
         <v>3.7</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="1">
+        <v>16.8</v>
+      </c>
       <c r="J103" s="1">
         <v>5</v>
       </c>
-      <c r="K103" s="1"/>
+      <c r="K103" s="1">
+        <v>3.6</v>
+      </c>
       <c r="L103" s="1">
         <v>2.7</v>
       </c>
-      <c r="M103" s="1"/>
+      <c r="M103" s="1">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E13CDD6-EE86-40C2-9784-3157F6112557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71DD4BC-D1BA-4BA7-B0D7-8B05D91552C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1696,23 +1696,34 @@
       <c r="D31" s="1">
         <v>45</v>
       </c>
-      <c r="E31" s="1"/>
+      <c r="E31" s="1">
+        <f>70.6+30.5</f>
+        <v>101.1</v>
+      </c>
       <c r="F31" s="1">
         <v>35.1</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>62.2</v>
+      </c>
       <c r="H31" s="1">
         <v>30</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>56.9</v>
+      </c>
       <c r="J31" s="1">
         <v>12</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="1">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="L31" s="1">
         <v>13.5</v>
       </c>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -1839,21 +1850,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1897,13 +1908,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1928,9 +1939,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3050,23 +3061,34 @@
       <c r="D68" s="1">
         <v>15</v>
       </c>
-      <c r="E68" s="1"/>
+      <c r="E68" s="1">
+        <f>20.1+14</f>
+        <v>34.1</v>
+      </c>
       <c r="F68" s="1">
         <v>10</v>
       </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="1">
+        <v>17.3</v>
+      </c>
       <c r="H68" s="1">
         <v>7.4</v>
       </c>
-      <c r="I68" s="1"/>
+      <c r="I68" s="1">
+        <v>15.8</v>
+      </c>
       <c r="J68" s="1">
         <v>8</v>
       </c>
-      <c r="K68" s="1"/>
+      <c r="K68" s="1">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="L68" s="1">
         <v>2.8</v>
       </c>
-      <c r="M68" s="1"/>
+      <c r="M68" s="1">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
@@ -3193,21 +3215,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3251,13 +3273,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3282,9 +3304,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3333,13 +3355,13 @@
         <v>34.799999999999997</v>
       </c>
       <c r="F78" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G78" s="1">
         <v>7.4</v>
       </c>
       <c r="H78" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I78" s="1">
         <v>6.4</v>
@@ -3374,13 +3396,13 @@
         <v>35.1</v>
       </c>
       <c r="F79" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G79" s="1">
         <v>7.4</v>
       </c>
       <c r="H79" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I79" s="1">
         <v>6.4</v>
@@ -3415,13 +3437,13 @@
         <v>48.2</v>
       </c>
       <c r="F80" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G80" s="1">
         <v>7.4</v>
       </c>
       <c r="H80" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I80" s="1">
         <v>6.4</v>
@@ -3457,13 +3479,13 @@
         <v>41.5</v>
       </c>
       <c r="F81" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G81" s="1">
         <v>5.9</v>
       </c>
       <c r="H81" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I81" s="1">
         <v>13.4</v>
@@ -3499,13 +3521,13 @@
         <v>44.6</v>
       </c>
       <c r="F82" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G82" s="1">
         <v>9.6999999999999993</v>
       </c>
       <c r="H82" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I82" s="1">
         <v>12.4</v>
@@ -3541,13 +3563,13 @@
         <v>35.6</v>
       </c>
       <c r="F83" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G83" s="1">
         <v>13.2</v>
       </c>
       <c r="H83" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I83" s="1">
         <v>11.7</v>
@@ -3583,13 +3605,13 @@
         <v>46.3</v>
       </c>
       <c r="F84" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G84" s="1">
         <v>11.4</v>
       </c>
       <c r="H84" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I84" s="1">
         <v>10.5</v>
@@ -3624,13 +3646,13 @@
         <v>38.799999999999997</v>
       </c>
       <c r="F85" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G85" s="1">
         <v>10</v>
       </c>
       <c r="H85" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I85" s="1">
         <v>9.3000000000000007</v>
@@ -3665,13 +3687,13 @@
         <v>39.200000000000003</v>
       </c>
       <c r="F86" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G86" s="1">
         <v>10.1</v>
       </c>
       <c r="H86" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I86" s="1">
         <v>9.3000000000000007</v>
@@ -3707,13 +3729,13 @@
         <v>39.200000000000003</v>
       </c>
       <c r="F87" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G87" s="1">
         <v>10.1</v>
       </c>
       <c r="H87" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I87" s="1">
         <v>9.3000000000000007</v>
@@ -3749,13 +3771,13 @@
         <v>41.9</v>
       </c>
       <c r="F88" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G88" s="1">
         <v>7.7</v>
       </c>
       <c r="H88" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I88" s="1">
         <v>6</v>
@@ -3791,13 +3813,13 @@
         <v>41.2</v>
       </c>
       <c r="F89" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G89" s="1">
         <v>12.5</v>
       </c>
       <c r="H89" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I89" s="1">
         <v>13.7</v>
@@ -3833,13 +3855,13 @@
         <v>35.4</v>
       </c>
       <c r="F90" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G90" s="1">
         <v>14</v>
       </c>
       <c r="H90" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I90" s="1">
         <v>13.1</v>
@@ -3875,13 +3897,13 @@
         <v>36</v>
       </c>
       <c r="F91" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G91" s="1">
         <v>12</v>
       </c>
       <c r="H91" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I91" s="1">
         <v>11.5</v>
@@ -3916,13 +3938,13 @@
         <v>27.1</v>
       </c>
       <c r="F92" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G92" s="1">
         <v>11.2</v>
       </c>
       <c r="H92" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I92" s="1">
         <v>9.1999999999999993</v>
@@ -3957,13 +3979,13 @@
         <v>27.6</v>
       </c>
       <c r="F93" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G93" s="1">
         <v>11.2</v>
       </c>
       <c r="H93" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I93" s="1">
         <v>9.1999999999999993</v>
@@ -3998,13 +4020,13 @@
         <v>48</v>
       </c>
       <c r="F94" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G94" s="1">
         <v>11.2</v>
       </c>
       <c r="H94" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I94" s="1">
         <v>9.1999999999999993</v>
@@ -4039,13 +4061,13 @@
         <v>36.5</v>
       </c>
       <c r="F95" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G95" s="1">
         <v>10.5</v>
       </c>
       <c r="H95" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I95" s="1">
         <v>6.3</v>
@@ -4081,13 +4103,13 @@
         <v>41.5</v>
       </c>
       <c r="F96" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G96" s="1">
         <v>11.3</v>
       </c>
       <c r="H96" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I96" s="1">
         <v>10.1</v>
@@ -4123,13 +4145,13 @@
         <v>41.7</v>
       </c>
       <c r="F97" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G97" s="1">
         <v>10.9</v>
       </c>
       <c r="H97" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I97" s="1">
         <v>9.1999999999999993</v>
@@ -4165,13 +4187,13 @@
         <v>39.4</v>
       </c>
       <c r="F98" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G98" s="1">
         <v>8.8000000000000007</v>
       </c>
       <c r="H98" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I98" s="1">
         <v>7.5</v>
@@ -4206,13 +4228,13 @@
         <v>32.700000000000003</v>
       </c>
       <c r="F99" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G99" s="1">
         <v>7.4</v>
       </c>
       <c r="H99" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I99" s="1">
         <v>6.4</v>
@@ -4247,13 +4269,13 @@
         <v>33.200000000000003</v>
       </c>
       <c r="F100" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G100" s="1">
         <v>7.1</v>
       </c>
       <c r="H100" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I100" s="1">
         <v>6.4</v>
@@ -4288,13 +4310,13 @@
         <v>39.9</v>
       </c>
       <c r="F101" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G101" s="1">
         <v>7.1</v>
       </c>
       <c r="H101" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I101" s="1">
         <v>6.4</v>
@@ -4330,13 +4352,13 @@
         <v>37.6</v>
       </c>
       <c r="F102" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G102" s="1">
         <v>5.6</v>
       </c>
       <c r="H102" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I102" s="1">
         <v>3.7</v>
@@ -4372,13 +4394,13 @@
         <v>49.9</v>
       </c>
       <c r="F103" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G103" s="1">
         <v>10.4</v>
       </c>
       <c r="H103" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I103" s="1">
         <v>16.8</v>
@@ -4409,23 +4431,34 @@
       <c r="D104" s="1">
         <v>22</v>
       </c>
-      <c r="E104" s="1"/>
+      <c r="E104" s="1">
+        <f>43.3+9</f>
+        <v>52.3</v>
+      </c>
       <c r="F104" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G104" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="G104" s="1">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="H104" s="1">
-        <v>3.7</v>
-      </c>
-      <c r="I104" s="1"/>
+        <v>4.5</v>
+      </c>
+      <c r="I104" s="1">
+        <v>16</v>
+      </c>
       <c r="J104" s="1">
         <v>5</v>
       </c>
-      <c r="K104" s="1"/>
+      <c r="K104" s="1">
+        <v>2.8</v>
+      </c>
       <c r="L104" s="1">
         <v>2.7</v>
       </c>
-      <c r="M104" s="1"/>
+      <c r="M104" s="1">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -4442,11 +4475,11 @@
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1">
@@ -4473,11 +4506,11 @@
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
@@ -4504,11 +4537,11 @@
       </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
@@ -4535,11 +4568,11 @@
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
@@ -4553,6 +4586,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4562,24 +4613,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71DD4BC-D1BA-4BA7-B0D7-8B05D91552C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCC4939-77D1-464F-9D38-18BD14BFD370}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1738,23 +1738,34 @@
       <c r="D32" s="1">
         <v>45</v>
       </c>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <f>95</f>
+        <v>95</v>
+      </c>
       <c r="F32" s="1">
         <v>35.1</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>51.5</v>
+      </c>
       <c r="H32" s="1">
         <v>30</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>49.4</v>
+      </c>
       <c r="J32" s="1">
         <v>12</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1">
+        <v>7.3</v>
+      </c>
       <c r="L32" s="1">
         <v>13.5</v>
       </c>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -1850,21 +1861,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1908,13 +1919,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1939,9 +1950,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3103,23 +3114,34 @@
       <c r="D69" s="1">
         <v>15</v>
       </c>
-      <c r="E69" s="1"/>
+      <c r="E69" s="1">
+        <f>27.5</f>
+        <v>27.5</v>
+      </c>
       <c r="F69" s="1">
         <v>10</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1">
+        <v>21.3</v>
+      </c>
       <c r="H69" s="1">
         <v>7.4</v>
       </c>
-      <c r="I69" s="1"/>
+      <c r="I69" s="1">
+        <v>19.7</v>
+      </c>
       <c r="J69" s="1">
         <v>8</v>
       </c>
-      <c r="K69" s="1"/>
+      <c r="K69" s="1">
+        <v>3.9</v>
+      </c>
       <c r="L69" s="1">
         <v>2.8</v>
       </c>
-      <c r="M69" s="1"/>
+      <c r="M69" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
@@ -3215,21 +3237,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3273,13 +3295,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3304,9 +3326,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4473,23 +4495,34 @@
       <c r="D105" s="1">
         <v>22</v>
       </c>
-      <c r="E105" s="1"/>
+      <c r="E105" s="1">
+        <f>43.2+5</f>
+        <v>48.2</v>
+      </c>
       <c r="F105" s="1">
         <v>6</v>
       </c>
-      <c r="G105" s="1"/>
+      <c r="G105" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H105" s="1">
         <v>4.5</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <v>14.9</v>
+      </c>
       <c r="J105" s="1">
         <v>5</v>
       </c>
-      <c r="K105" s="1"/>
+      <c r="K105" s="1">
+        <v>2.4</v>
+      </c>
       <c r="L105" s="1">
         <v>2.7</v>
       </c>
-      <c r="M105" s="1"/>
+      <c r="M105" s="1">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -4586,6 +4619,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4595,24 +4646,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="C76:C77"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(08,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCC4939-77D1-464F-9D38-18BD14BFD370}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4392F8-7B2D-4AFC-AA82-DB80E035B1A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1780,23 +1780,33 @@
       <c r="D33" s="1">
         <v>45</v>
       </c>
-      <c r="E33" s="1"/>
+      <c r="E33" s="1">
+        <v>68.3</v>
+      </c>
       <c r="F33" s="1">
         <v>35.1</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>43.9</v>
+      </c>
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>60.6</v>
+      </c>
       <c r="J33" s="1">
         <v>12</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1">
+        <v>5.2</v>
+      </c>
       <c r="L33" s="1">
         <v>13.5</v>
       </c>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -1811,23 +1821,33 @@
       <c r="D34" s="1">
         <v>45</v>
       </c>
-      <c r="E34" s="1"/>
+      <c r="E34" s="1">
+        <v>68.900000000000006</v>
+      </c>
       <c r="F34" s="1">
         <v>35.1</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1">
+        <v>43.9</v>
+      </c>
       <c r="H34" s="1">
         <v>30</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1">
+        <v>60.1</v>
+      </c>
       <c r="J34" s="1">
         <v>12</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1">
+        <v>5.3</v>
+      </c>
       <c r="L34" s="1">
         <v>13.5</v>
       </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -1842,40 +1862,51 @@
       <c r="D35" s="1">
         <v>45</v>
       </c>
-      <c r="E35" s="1"/>
+      <c r="E35" s="1">
+        <f>68.9+35</f>
+        <v>103.9</v>
+      </c>
       <c r="F35" s="1">
         <v>35.1</v>
       </c>
-      <c r="G35" s="1"/>
+      <c r="G35" s="1">
+        <v>43.9</v>
+      </c>
       <c r="H35" s="1">
         <v>30</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1">
+        <v>60.1</v>
+      </c>
       <c r="J35" s="1">
         <v>12</v>
       </c>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L35" s="1">
         <v>13.5</v>
       </c>
-      <c r="M35" s="1"/>
+      <c r="M35" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1919,13 +1950,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1950,9 +1981,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3156,23 +3187,33 @@
       <c r="D70" s="1">
         <v>15</v>
       </c>
-      <c r="E70" s="1"/>
+      <c r="E70" s="1">
+        <v>22.5</v>
+      </c>
       <c r="F70" s="1">
         <v>10</v>
       </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>17.8</v>
+      </c>
       <c r="H70" s="1">
         <v>7.4</v>
       </c>
-      <c r="I70" s="1"/>
+      <c r="I70" s="1">
+        <v>18.899999999999999</v>
+      </c>
       <c r="J70" s="1">
         <v>8</v>
       </c>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L70" s="1">
         <v>2.8</v>
       </c>
-      <c r="M70" s="1"/>
+      <c r="M70" s="1">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
@@ -3187,23 +3228,33 @@
       <c r="D71" s="1">
         <v>15</v>
       </c>
-      <c r="E71" s="1"/>
+      <c r="E71" s="1">
+        <v>22.8</v>
+      </c>
       <c r="F71" s="1">
         <v>10</v>
       </c>
-      <c r="G71" s="1"/>
+      <c r="G71" s="1">
+        <v>14.9</v>
+      </c>
       <c r="H71" s="1">
         <v>7.4</v>
       </c>
-      <c r="I71" s="1"/>
+      <c r="I71" s="1">
+        <v>17.7</v>
+      </c>
       <c r="J71" s="1">
         <v>8</v>
       </c>
-      <c r="K71" s="1"/>
+      <c r="K71" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L71" s="1">
         <v>2.8</v>
       </c>
-      <c r="M71" s="1"/>
+      <c r="M71" s="1">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
@@ -3218,40 +3269,51 @@
       <c r="D72" s="1">
         <v>15</v>
       </c>
-      <c r="E72" s="1"/>
+      <c r="E72" s="1">
+        <f>39.9</f>
+        <v>39.9</v>
+      </c>
       <c r="F72" s="1">
         <v>10</v>
       </c>
-      <c r="G72" s="1"/>
+      <c r="G72" s="1">
+        <v>14.9</v>
+      </c>
       <c r="H72" s="1">
         <v>7.4</v>
       </c>
-      <c r="I72" s="1"/>
+      <c r="I72" s="1">
+        <v>17.7</v>
+      </c>
       <c r="J72" s="1">
         <v>8</v>
       </c>
-      <c r="K72" s="1"/>
+      <c r="K72" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L72" s="1">
         <v>2.8</v>
       </c>
-      <c r="M72" s="1"/>
+      <c r="M72" s="1">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3295,13 +3357,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -3326,9 +3388,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4537,23 +4599,33 @@
       <c r="D106" s="1">
         <v>22</v>
       </c>
-      <c r="E106" s="1"/>
+      <c r="E106" s="1">
+        <v>41.2</v>
+      </c>
       <c r="F106" s="1">
         <v>6</v>
       </c>
-      <c r="G106" s="1"/>
+      <c r="G106" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="H106" s="1">
         <v>4.5</v>
       </c>
-      <c r="I106" s="1"/>
+      <c r="I106" s="1">
+        <v>13.4</v>
+      </c>
       <c r="J106" s="1">
         <v>5</v>
       </c>
-      <c r="K106" s="1"/>
+      <c r="K106" s="1">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="L106" s="1">
         <v>2.7</v>
       </c>
-      <c r="M106" s="1"/>
+      <c r="M106" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -4568,23 +4640,33 @@
       <c r="D107" s="1">
         <v>22</v>
       </c>
-      <c r="E107" s="1"/>
+      <c r="E107" s="1">
+        <v>41.5</v>
+      </c>
       <c r="F107" s="1">
         <v>6</v>
       </c>
-      <c r="G107" s="1"/>
+      <c r="G107" s="1">
+        <v>10.4</v>
+      </c>
       <c r="H107" s="1">
         <v>4.5</v>
       </c>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <v>13.4</v>
+      </c>
       <c r="J107" s="1">
         <v>5</v>
       </c>
-      <c r="K107" s="1"/>
+      <c r="K107" s="1">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="L107" s="1">
         <v>2.7</v>
       </c>
-      <c r="M107" s="1"/>
+      <c r="M107" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -4599,26 +4681,55 @@
       <c r="D108" s="1">
         <v>22</v>
       </c>
-      <c r="E108" s="1"/>
+      <c r="E108" s="1">
+        <f>45.8</f>
+        <v>45.8</v>
+      </c>
       <c r="F108" s="1">
         <v>6</v>
       </c>
-      <c r="G108" s="1"/>
+      <c r="G108" s="1">
+        <v>10.4</v>
+      </c>
       <c r="H108" s="1">
         <v>4.5</v>
       </c>
-      <c r="I108" s="1"/>
+      <c r="I108" s="1">
+        <v>13.4</v>
+      </c>
       <c r="J108" s="1">
         <v>5</v>
       </c>
-      <c r="K108" s="1"/>
+      <c r="K108" s="1">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="L108" s="1">
         <v>2.7</v>
       </c>
-      <c r="M108" s="1"/>
+      <c r="M108" s="1">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -4628,24 +4739,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
